--- a/1차 프로젝트/기획/개발 스케줄.xlsx
+++ b/1차 프로젝트/기획/개발 스케줄.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\act6h\Desktop\project_1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\[GitHub]\LeeSeungChan\1차 프로젝트\기획\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5DA34ED-761D-4C4F-A4B0-94CDB6F5870F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F03C61C6-DE62-41F9-983E-DEEBEAE46A9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{A6426BF2-C243-4278-99EB-5A9494FEB86F}"/>
   </bookViews>
@@ -616,6 +616,36 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -632,36 +662,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1009,56 +1009,56 @@
   <sheetData>
     <row r="3" spans="2:36" ht="17.5" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="4" spans="2:36" x14ac:dyDescent="0.45">
-      <c r="B4" s="37" t="s">
+      <c r="B4" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="39" t="s">
+      <c r="C4" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="41" t="s">
+      <c r="D4" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="33" t="s">
+      <c r="E4" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="F4" s="34"/>
-      <c r="G4" s="34"/>
-      <c r="H4" s="34"/>
-      <c r="I4" s="34"/>
-      <c r="J4" s="34"/>
-      <c r="K4" s="34"/>
-      <c r="L4" s="34"/>
-      <c r="M4" s="34"/>
-      <c r="N4" s="34"/>
-      <c r="O4" s="34"/>
-      <c r="P4" s="34"/>
-      <c r="Q4" s="34"/>
-      <c r="R4" s="34"/>
-      <c r="S4" s="35"/>
-      <c r="T4" s="33" t="s">
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
+      <c r="H4" s="28"/>
+      <c r="I4" s="28"/>
+      <c r="J4" s="28"/>
+      <c r="K4" s="28"/>
+      <c r="L4" s="28"/>
+      <c r="M4" s="28"/>
+      <c r="N4" s="28"/>
+      <c r="O4" s="28"/>
+      <c r="P4" s="28"/>
+      <c r="Q4" s="28"/>
+      <c r="R4" s="28"/>
+      <c r="S4" s="29"/>
+      <c r="T4" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="U4" s="34"/>
-      <c r="V4" s="34"/>
-      <c r="W4" s="34"/>
-      <c r="X4" s="34"/>
-      <c r="Y4" s="34"/>
-      <c r="Z4" s="34"/>
-      <c r="AA4" s="34"/>
-      <c r="AB4" s="34"/>
-      <c r="AC4" s="34"/>
-      <c r="AD4" s="34"/>
-      <c r="AE4" s="34"/>
-      <c r="AF4" s="34"/>
-      <c r="AG4" s="34"/>
-      <c r="AH4" s="34"/>
-      <c r="AI4" s="34"/>
-      <c r="AJ4" s="36"/>
+      <c r="U4" s="28"/>
+      <c r="V4" s="28"/>
+      <c r="W4" s="28"/>
+      <c r="X4" s="28"/>
+      <c r="Y4" s="28"/>
+      <c r="Z4" s="28"/>
+      <c r="AA4" s="28"/>
+      <c r="AB4" s="28"/>
+      <c r="AC4" s="28"/>
+      <c r="AD4" s="28"/>
+      <c r="AE4" s="28"/>
+      <c r="AF4" s="28"/>
+      <c r="AG4" s="28"/>
+      <c r="AH4" s="28"/>
+      <c r="AI4" s="28"/>
+      <c r="AJ4" s="30"/>
     </row>
     <row r="5" spans="2:36" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B5" s="38"/>
-      <c r="C5" s="40"/>
-      <c r="D5" s="42"/>
+      <c r="B5" s="32"/>
+      <c r="C5" s="34"/>
+      <c r="D5" s="36"/>
       <c r="E5" s="12">
         <v>17</v>
       </c>
@@ -1157,7 +1157,7 @@
       </c>
     </row>
     <row r="6" spans="2:36" ht="17" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="B6" s="27" t="s">
+      <c r="B6" s="37" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="19">
@@ -1199,7 +1199,7 @@
       <c r="AJ6" s="4"/>
     </row>
     <row r="7" spans="2:36" x14ac:dyDescent="0.45">
-      <c r="B7" s="28"/>
+      <c r="B7" s="38"/>
       <c r="C7" s="6">
         <v>1.2</v>
       </c>
@@ -1237,7 +1237,7 @@
       <c r="AJ7" s="4"/>
     </row>
     <row r="8" spans="2:36" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B8" s="28"/>
+      <c r="B8" s="38"/>
       <c r="C8" s="8">
         <v>1.3</v>
       </c>
@@ -1278,7 +1278,7 @@
       <c r="AJ8" s="4"/>
     </row>
     <row r="9" spans="2:36" ht="17" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B9" s="29" t="s">
+      <c r="B9" s="39" t="s">
         <v>8</v>
       </c>
       <c r="C9" s="21">
@@ -1321,7 +1321,7 @@
       <c r="AJ9" s="4"/>
     </row>
     <row r="10" spans="2:36" x14ac:dyDescent="0.45">
-      <c r="B10" s="28"/>
+      <c r="B10" s="38"/>
       <c r="C10" s="6">
         <v>2.2000000000000002</v>
       </c>
@@ -1362,7 +1362,7 @@
       <c r="AJ10" s="4"/>
     </row>
     <row r="11" spans="2:36" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B11" s="30"/>
+      <c r="B11" s="40"/>
       <c r="C11" s="8">
         <v>2.2999999999999998</v>
       </c>
@@ -1402,14 +1402,14 @@
       <c r="AJ11" s="4"/>
     </row>
     <row r="12" spans="2:36" x14ac:dyDescent="0.45">
-      <c r="B12" s="28" t="s">
-        <v>13</v>
+      <c r="B12" s="39" t="s">
+        <v>22</v>
       </c>
       <c r="C12" s="21">
         <v>3.1</v>
       </c>
-      <c r="D12" s="23" t="s">
-        <v>18</v>
+      <c r="D12" s="20" t="s">
+        <v>14</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="2"/>
@@ -1427,29 +1427,20 @@
       <c r="R12" s="10"/>
       <c r="S12" s="2"/>
       <c r="T12" s="1"/>
-      <c r="V12" s="2"/>
-      <c r="W12" s="2"/>
       <c r="X12" s="2"/>
       <c r="Y12" s="2"/>
-      <c r="Z12" s="2"/>
-      <c r="AA12" s="2"/>
-      <c r="AB12" s="2"/>
-      <c r="AC12" s="2"/>
-      <c r="AD12" s="2"/>
-      <c r="AE12" s="2"/>
-      <c r="AF12" s="2"/>
       <c r="AG12" s="2"/>
       <c r="AH12" s="2"/>
       <c r="AI12" s="2"/>
       <c r="AJ12" s="4"/>
     </row>
     <row r="13" spans="2:36" x14ac:dyDescent="0.45">
-      <c r="B13" s="28"/>
+      <c r="B13" s="38"/>
       <c r="C13" s="6">
         <v>3.2</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>19</v>
+      <c r="D13" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="2"/>
@@ -1467,27 +1458,21 @@
       <c r="R13" s="2"/>
       <c r="S13" s="10"/>
       <c r="T13" s="11"/>
-      <c r="U13" s="10"/>
+      <c r="U13" s="2"/>
+      <c r="X13" s="2"/>
       <c r="Y13" s="2"/>
-      <c r="Z13" s="2"/>
-      <c r="AA13" s="2"/>
-      <c r="AB13" s="2"/>
-      <c r="AC13" s="2"/>
-      <c r="AD13" s="2"/>
-      <c r="AE13" s="2"/>
-      <c r="AF13" s="2"/>
       <c r="AG13" s="2"/>
       <c r="AH13" s="2"/>
       <c r="AI13" s="2"/>
       <c r="AJ13" s="4"/>
     </row>
     <row r="14" spans="2:36" x14ac:dyDescent="0.45">
-      <c r="B14" s="28"/>
+      <c r="B14" s="38"/>
       <c r="C14" s="6">
         <v>3.3</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>20</v>
+      <c r="D14" s="7" t="s">
+        <v>16</v>
       </c>
       <c r="E14" s="1"/>
       <c r="F14" s="2"/>
@@ -1501,29 +1486,24 @@
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" s="2"/>
-      <c r="Q14" s="2"/>
-      <c r="R14" s="2"/>
       <c r="S14" s="2"/>
       <c r="T14" s="1"/>
-      <c r="U14" s="2"/>
+      <c r="U14" s="10"/>
       <c r="V14" s="10"/>
-      <c r="W14" s="10"/>
       <c r="X14" s="2"/>
-      <c r="AA14" s="2"/>
-      <c r="AE14" s="2"/>
-      <c r="AF14" s="2"/>
+      <c r="Y14" s="2"/>
       <c r="AG14" s="2"/>
       <c r="AH14" s="2"/>
       <c r="AI14" s="2"/>
       <c r="AJ14" s="4"/>
     </row>
     <row r="15" spans="2:36" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B15" s="28"/>
+      <c r="B15" s="40"/>
       <c r="C15" s="8">
         <v>3.4</v>
       </c>
-      <c r="D15" s="5" t="s">
-        <v>21</v>
+      <c r="D15" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="E15" s="1"/>
       <c r="F15" s="2"/>
@@ -1537,34 +1517,27 @@
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
       <c r="P15" s="2"/>
-      <c r="Q15" s="2"/>
-      <c r="R15" s="2"/>
       <c r="S15" s="2"/>
       <c r="T15" s="1"/>
       <c r="U15" s="2"/>
-      <c r="V15" s="2"/>
-      <c r="W15" s="2"/>
-      <c r="X15" s="10"/>
-      <c r="Y15" s="10"/>
-      <c r="AB15" s="2"/>
-      <c r="AC15" s="2"/>
-      <c r="AD15" s="2"/>
-      <c r="AE15" s="2"/>
-      <c r="AF15" s="2"/>
+      <c r="V15" s="10"/>
+      <c r="W15" s="10"/>
+      <c r="X15" s="2"/>
+      <c r="Y15" s="2"/>
       <c r="AG15" s="2"/>
       <c r="AH15" s="2"/>
       <c r="AI15" s="2"/>
       <c r="AJ15" s="4"/>
     </row>
     <row r="16" spans="2:36" x14ac:dyDescent="0.45">
-      <c r="B16" s="29" t="s">
-        <v>22</v>
+      <c r="B16" s="39" t="s">
+        <v>13</v>
       </c>
       <c r="C16" s="21">
         <v>4.0999999999999996</v>
       </c>
-      <c r="D16" s="20" t="s">
-        <v>14</v>
+      <c r="D16" s="23" t="s">
+        <v>18</v>
       </c>
       <c r="E16" s="1"/>
       <c r="F16" s="2"/>
@@ -1578,31 +1551,27 @@
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
       <c r="P16" s="2"/>
-      <c r="Q16" s="2"/>
-      <c r="R16" s="2"/>
-      <c r="S16" s="2"/>
       <c r="T16" s="1"/>
-      <c r="U16" s="2"/>
-      <c r="V16" s="2"/>
-      <c r="W16" s="2"/>
-      <c r="X16" s="2"/>
-      <c r="Y16" s="2"/>
-      <c r="Z16" s="10"/>
-      <c r="AA16" s="10"/>
-      <c r="AB16" s="2"/>
+      <c r="X16" s="10"/>
+      <c r="Y16" s="10"/>
+      <c r="Z16" s="2"/>
+      <c r="AA16" s="2"/>
       <c r="AC16" s="2"/>
+      <c r="AD16" s="2"/>
+      <c r="AE16" s="2"/>
+      <c r="AF16" s="2"/>
       <c r="AG16" s="2"/>
       <c r="AH16" s="2"/>
       <c r="AI16" s="2"/>
       <c r="AJ16" s="4"/>
     </row>
     <row r="17" spans="2:36" x14ac:dyDescent="0.45">
-      <c r="B17" s="28"/>
+      <c r="B17" s="38"/>
       <c r="C17" s="6">
         <v>4.2</v>
       </c>
-      <c r="D17" s="7" t="s">
-        <v>15</v>
+      <c r="D17" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="E17" s="1"/>
       <c r="F17" s="2"/>
@@ -1616,32 +1585,25 @@
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
       <c r="P17" s="2"/>
-      <c r="Q17" s="2"/>
-      <c r="R17" s="2"/>
-      <c r="S17" s="2"/>
       <c r="T17" s="1"/>
-      <c r="U17" s="2"/>
-      <c r="V17" s="2"/>
-      <c r="W17" s="2"/>
       <c r="X17" s="2"/>
       <c r="Y17" s="2"/>
-      <c r="Z17" s="2"/>
-      <c r="AA17" s="2"/>
+      <c r="Z17" s="10"/>
+      <c r="AA17" s="10"/>
       <c r="AB17" s="10"/>
-      <c r="AC17" s="10"/>
-      <c r="AD17" s="2"/>
+      <c r="AF17" s="2"/>
       <c r="AG17" s="2"/>
       <c r="AH17" s="2"/>
       <c r="AI17" s="2"/>
       <c r="AJ17" s="4"/>
     </row>
     <row r="18" spans="2:36" x14ac:dyDescent="0.45">
-      <c r="B18" s="28"/>
+      <c r="B18" s="38"/>
       <c r="C18" s="6">
         <v>4.3</v>
       </c>
-      <c r="D18" s="7" t="s">
-        <v>16</v>
+      <c r="D18" s="3" t="s">
+        <v>20</v>
       </c>
       <c r="E18" s="1"/>
       <c r="F18" s="2"/>
@@ -1655,31 +1617,27 @@
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" s="2"/>
-      <c r="Q18" s="2"/>
-      <c r="R18" s="2"/>
-      <c r="S18" s="2"/>
       <c r="T18" s="1"/>
-      <c r="U18" s="2"/>
-      <c r="V18" s="2"/>
-      <c r="W18" s="2"/>
       <c r="X18" s="2"/>
       <c r="Y18" s="2"/>
+      <c r="Z18" s="2"/>
+      <c r="AA18" s="2"/>
       <c r="AB18" s="2"/>
-      <c r="AC18" s="2"/>
+      <c r="AC18" s="10"/>
       <c r="AD18" s="10"/>
-      <c r="AE18" s="10"/>
+      <c r="AE18" s="2"/>
       <c r="AG18" s="2"/>
       <c r="AH18" s="2"/>
       <c r="AI18" s="2"/>
       <c r="AJ18" s="4"/>
     </row>
     <row r="19" spans="2:36" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B19" s="30"/>
+      <c r="B19" s="40"/>
       <c r="C19" s="8">
         <v>4.4000000000000004</v>
       </c>
-      <c r="D19" s="9" t="s">
-        <v>17</v>
+      <c r="D19" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="E19" s="1"/>
       <c r="F19" s="2"/>
@@ -1693,16 +1651,13 @@
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" s="2"/>
-      <c r="Q19" s="2"/>
-      <c r="R19" s="2"/>
-      <c r="S19" s="2"/>
       <c r="T19" s="1"/>
-      <c r="U19" s="2"/>
-      <c r="V19" s="2"/>
-      <c r="W19" s="2"/>
       <c r="X19" s="2"/>
       <c r="Y19" s="2"/>
+      <c r="Z19" s="2"/>
+      <c r="AA19" s="2"/>
       <c r="AB19" s="2"/>
+      <c r="AC19" s="2"/>
       <c r="AD19" s="2"/>
       <c r="AE19" s="10"/>
       <c r="AF19" s="10"/>
@@ -1712,7 +1667,7 @@
       <c r="AJ19" s="4"/>
     </row>
     <row r="20" spans="2:36" x14ac:dyDescent="0.45">
-      <c r="B20" s="31" t="s">
+      <c r="B20" s="41" t="s">
         <v>26</v>
       </c>
       <c r="C20" s="21">
@@ -1755,7 +1710,7 @@
       <c r="AJ20" s="18"/>
     </row>
     <row r="21" spans="2:36" x14ac:dyDescent="0.45">
-      <c r="B21" s="31"/>
+      <c r="B21" s="41"/>
       <c r="C21" s="6">
         <v>5.2</v>
       </c>
@@ -1796,7 +1751,7 @@
       <c r="AJ21" s="18"/>
     </row>
     <row r="22" spans="2:36" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B22" s="32"/>
+      <c r="B22" s="42"/>
       <c r="C22" s="8">
         <v>5.3</v>
       </c>
@@ -1838,16 +1793,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B6:B8"/>
+    <mergeCell ref="B16:B19"/>
+    <mergeCell ref="B12:B15"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="B9:B11"/>
     <mergeCell ref="E4:S4"/>
     <mergeCell ref="T4:AJ4"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="C4:C5"/>
     <mergeCell ref="D4:D5"/>
-    <mergeCell ref="B6:B8"/>
-    <mergeCell ref="B12:B15"/>
-    <mergeCell ref="B16:B19"/>
-    <mergeCell ref="B20:B22"/>
-    <mergeCell ref="B9:B11"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/1차 프로젝트/기획/개발 스케줄.xlsx
+++ b/1차 프로젝트/기획/개발 스케줄.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\[GitHub]\LeeSeungChan\1차 프로젝트\기획\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F03C61C6-DE62-41F9-983E-DEEBEAE46A9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACFE81D0-D42C-4D4B-90BF-025D096E9B46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{A6426BF2-C243-4278-99EB-5A9494FEB86F}"/>
   </bookViews>
@@ -616,6 +616,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -644,24 +662,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1009,56 +1009,56 @@
   <sheetData>
     <row r="3" spans="2:36" ht="17.5" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="4" spans="2:36" x14ac:dyDescent="0.45">
-      <c r="B4" s="31" t="s">
+      <c r="B4" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="33" t="s">
+      <c r="C4" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="35" t="s">
+      <c r="D4" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="27" t="s">
+      <c r="E4" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="F4" s="28"/>
-      <c r="G4" s="28"/>
-      <c r="H4" s="28"/>
-      <c r="I4" s="28"/>
-      <c r="J4" s="28"/>
-      <c r="K4" s="28"/>
-      <c r="L4" s="28"/>
-      <c r="M4" s="28"/>
-      <c r="N4" s="28"/>
-      <c r="O4" s="28"/>
-      <c r="P4" s="28"/>
-      <c r="Q4" s="28"/>
-      <c r="R4" s="28"/>
-      <c r="S4" s="29"/>
-      <c r="T4" s="27" t="s">
+      <c r="F4" s="34"/>
+      <c r="G4" s="34"/>
+      <c r="H4" s="34"/>
+      <c r="I4" s="34"/>
+      <c r="J4" s="34"/>
+      <c r="K4" s="34"/>
+      <c r="L4" s="34"/>
+      <c r="M4" s="34"/>
+      <c r="N4" s="34"/>
+      <c r="O4" s="34"/>
+      <c r="P4" s="34"/>
+      <c r="Q4" s="34"/>
+      <c r="R4" s="34"/>
+      <c r="S4" s="35"/>
+      <c r="T4" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="U4" s="28"/>
-      <c r="V4" s="28"/>
-      <c r="W4" s="28"/>
-      <c r="X4" s="28"/>
-      <c r="Y4" s="28"/>
-      <c r="Z4" s="28"/>
-      <c r="AA4" s="28"/>
-      <c r="AB4" s="28"/>
-      <c r="AC4" s="28"/>
-      <c r="AD4" s="28"/>
-      <c r="AE4" s="28"/>
-      <c r="AF4" s="28"/>
-      <c r="AG4" s="28"/>
-      <c r="AH4" s="28"/>
-      <c r="AI4" s="28"/>
-      <c r="AJ4" s="30"/>
+      <c r="U4" s="34"/>
+      <c r="V4" s="34"/>
+      <c r="W4" s="34"/>
+      <c r="X4" s="34"/>
+      <c r="Y4" s="34"/>
+      <c r="Z4" s="34"/>
+      <c r="AA4" s="34"/>
+      <c r="AB4" s="34"/>
+      <c r="AC4" s="34"/>
+      <c r="AD4" s="34"/>
+      <c r="AE4" s="34"/>
+      <c r="AF4" s="34"/>
+      <c r="AG4" s="34"/>
+      <c r="AH4" s="34"/>
+      <c r="AI4" s="34"/>
+      <c r="AJ4" s="36"/>
     </row>
     <row r="5" spans="2:36" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B5" s="32"/>
-      <c r="C5" s="34"/>
-      <c r="D5" s="36"/>
+      <c r="B5" s="38"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="42"/>
       <c r="E5" s="12">
         <v>17</v>
       </c>
@@ -1157,7 +1157,7 @@
       </c>
     </row>
     <row r="6" spans="2:36" ht="17" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="B6" s="37" t="s">
+      <c r="B6" s="27" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="19">
@@ -1199,7 +1199,7 @@
       <c r="AJ6" s="4"/>
     </row>
     <row r="7" spans="2:36" x14ac:dyDescent="0.45">
-      <c r="B7" s="38"/>
+      <c r="B7" s="28"/>
       <c r="C7" s="6">
         <v>1.2</v>
       </c>
@@ -1237,7 +1237,7 @@
       <c r="AJ7" s="4"/>
     </row>
     <row r="8" spans="2:36" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B8" s="38"/>
+      <c r="B8" s="28"/>
       <c r="C8" s="8">
         <v>1.3</v>
       </c>
@@ -1278,7 +1278,7 @@
       <c r="AJ8" s="4"/>
     </row>
     <row r="9" spans="2:36" ht="17" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B9" s="39" t="s">
+      <c r="B9" s="29" t="s">
         <v>8</v>
       </c>
       <c r="C9" s="21">
@@ -1321,7 +1321,7 @@
       <c r="AJ9" s="4"/>
     </row>
     <row r="10" spans="2:36" x14ac:dyDescent="0.45">
-      <c r="B10" s="38"/>
+      <c r="B10" s="28"/>
       <c r="C10" s="6">
         <v>2.2000000000000002</v>
       </c>
@@ -1362,7 +1362,7 @@
       <c r="AJ10" s="4"/>
     </row>
     <row r="11" spans="2:36" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B11" s="40"/>
+      <c r="B11" s="30"/>
       <c r="C11" s="8">
         <v>2.2999999999999998</v>
       </c>
@@ -1402,7 +1402,7 @@
       <c r="AJ11" s="4"/>
     </row>
     <row r="12" spans="2:36" x14ac:dyDescent="0.45">
-      <c r="B12" s="39" t="s">
+      <c r="B12" s="29" t="s">
         <v>22</v>
       </c>
       <c r="C12" s="21">
@@ -1435,7 +1435,7 @@
       <c r="AJ12" s="4"/>
     </row>
     <row r="13" spans="2:36" x14ac:dyDescent="0.45">
-      <c r="B13" s="38"/>
+      <c r="B13" s="28"/>
       <c r="C13" s="6">
         <v>3.2</v>
       </c>
@@ -1467,7 +1467,7 @@
       <c r="AJ13" s="4"/>
     </row>
     <row r="14" spans="2:36" x14ac:dyDescent="0.45">
-      <c r="B14" s="38"/>
+      <c r="B14" s="28"/>
       <c r="C14" s="6">
         <v>3.3</v>
       </c>
@@ -1498,7 +1498,7 @@
       <c r="AJ14" s="4"/>
     </row>
     <row r="15" spans="2:36" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B15" s="40"/>
+      <c r="B15" s="30"/>
       <c r="C15" s="8">
         <v>3.4</v>
       </c>
@@ -1530,7 +1530,7 @@
       <c r="AJ15" s="4"/>
     </row>
     <row r="16" spans="2:36" x14ac:dyDescent="0.45">
-      <c r="B16" s="39" t="s">
+      <c r="B16" s="29" t="s">
         <v>13</v>
       </c>
       <c r="C16" s="21">
@@ -1566,7 +1566,7 @@
       <c r="AJ16" s="4"/>
     </row>
     <row r="17" spans="2:36" x14ac:dyDescent="0.45">
-      <c r="B17" s="38"/>
+      <c r="B17" s="28"/>
       <c r="C17" s="6">
         <v>4.2</v>
       </c>
@@ -1598,7 +1598,7 @@
       <c r="AJ17" s="4"/>
     </row>
     <row r="18" spans="2:36" x14ac:dyDescent="0.45">
-      <c r="B18" s="38"/>
+      <c r="B18" s="28"/>
       <c r="C18" s="6">
         <v>4.3</v>
       </c>
@@ -1632,7 +1632,7 @@
       <c r="AJ18" s="4"/>
     </row>
     <row r="19" spans="2:36" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B19" s="40"/>
+      <c r="B19" s="30"/>
       <c r="C19" s="8">
         <v>4.4000000000000004</v>
       </c>
@@ -1667,7 +1667,7 @@
       <c r="AJ19" s="4"/>
     </row>
     <row r="20" spans="2:36" x14ac:dyDescent="0.45">
-      <c r="B20" s="41" t="s">
+      <c r="B20" s="31" t="s">
         <v>26</v>
       </c>
       <c r="C20" s="21">
@@ -1710,7 +1710,7 @@
       <c r="AJ20" s="18"/>
     </row>
     <row r="21" spans="2:36" x14ac:dyDescent="0.45">
-      <c r="B21" s="41"/>
+      <c r="B21" s="31"/>
       <c r="C21" s="6">
         <v>5.2</v>
       </c>
@@ -1751,7 +1751,7 @@
       <c r="AJ21" s="18"/>
     </row>
     <row r="22" spans="2:36" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B22" s="42"/>
+      <c r="B22" s="32"/>
       <c r="C22" s="8">
         <v>5.3</v>
       </c>
@@ -1793,16 +1793,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="E4:S4"/>
+    <mergeCell ref="T4:AJ4"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
     <mergeCell ref="B6:B8"/>
     <mergeCell ref="B16:B19"/>
     <mergeCell ref="B12:B15"/>
     <mergeCell ref="B20:B22"/>
     <mergeCell ref="B9:B11"/>
-    <mergeCell ref="E4:S4"/>
-    <mergeCell ref="T4:AJ4"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
